--- a/data/trans_orig/Q5405-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5405-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar un telefono en 2007</t>
+          <t>Población según si es capaz de usar un telefono en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2080</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5798</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>19,52%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>897</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4678</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4040</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>15,75%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3936</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>833</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>932</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51914</t>
+          <t>51903</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58941</t>
+          <t>58951</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23362</t>
+          <t>23299</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>79890</t>
+          <t>78760</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87838</t>
+          <t>87749</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,62 +1224,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1751</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>8572</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1751</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>8807</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,62 +1337,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>3844</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>4265</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42002</t>
+          <t>41109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56672</t>
+          <t>56559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62468</t>
+          <t>62508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70089</t>
+          <t>70046</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18679</t>
+          <t>18282</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84318</t>
+          <t>84341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93458</t>
+          <t>93483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>22356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>237909</t>
+          <t>238654</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>252461</t>
+          <t>252045</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>74778</t>
+          <t>74849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83834</t>
+          <t>83869</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>317215</t>
+          <t>316075</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>334616</t>
+          <t>333088</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>11195</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>9074</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48150</t>
+          <t>47661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55465</t>
+          <t>54641</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84157</t>
+          <t>83249</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93995</t>
+          <t>93949</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135959</t>
+          <t>135510</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>147332</t>
+          <t>148016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>19765</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19956</t>
+          <t>19892</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>19992</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>19059</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>392319</t>
+          <t>391633</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>410461</t>
+          <t>411071</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>394219</t>
+          <t>396420</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>413875</t>
+          <t>415365</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14628</t>
+          <t>15151</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>11881</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29483</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16863</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38686</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>11743</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27743</t>
+          <t>28554</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>26295</t>
+          <t>26613</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>50080</t>
+          <t>49867</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>464544</t>
+          <t>463495</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>484426</t>
+          <t>483789</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>626513</t>
+          <t>626134</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>650828</t>
+          <t>650983</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1099205</t>
+          <t>1098117</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1129860</t>
+          <t>1128875</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar un telefono en 2012</t>
+          <t>Población según si es capaz de usar un telefono en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,62 +4194,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5683</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6058</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -4272,97 +4272,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2151</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4801</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5978</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5506</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>23,64%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>5587</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39353</t>
+          <t>37575</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61891</t>
+          <t>62143</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47163</t>
+          <t>47240</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59345</t>
+          <t>59203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64039</t>
+          <t>63106</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76298</t>
+          <t>76349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104310</t>
+          <t>104389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116766</t>
+          <t>117539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49220</t>
+          <t>49219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157888</t>
+          <t>158063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>171164</t>
+          <t>171178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18119</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20229</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11947</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32427</t>
+          <t>31278</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31668</t>
+          <t>33141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>189540</t>
+          <t>190391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211024</t>
+          <t>212540</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51249</t>
+          <t>51639</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59018</t>
+          <t>59014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>246531</t>
+          <t>246330</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>269061</t>
+          <t>268826</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>13444</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19986</t>
+          <t>20006</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26919</t>
+          <t>27505</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15038</t>
+          <t>14817</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29869</t>
+          <t>29769</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>39986</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80940</t>
+          <t>80689</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94394</t>
+          <t>94480</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>145420</t>
+          <t>146476</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>166945</t>
+          <t>166574</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>231225</t>
+          <t>231742</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>256635</t>
+          <t>256634</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25348</t>
+          <t>26066</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8267</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>25713</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33798</t>
+          <t>33167</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13802</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32970</t>
+          <t>32105</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>342435</t>
+          <t>342811</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>367483</t>
+          <t>367890</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>344162</t>
+          <t>346134</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>369373</t>
+          <t>370055</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29804</t>
+          <t>29849</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>21560</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45948</t>
+          <t>43958</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37599</t>
+          <t>36914</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>66962</t>
+          <t>65792</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24857</t>
+          <t>24726</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>51864</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34937</t>
+          <t>33906</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>61459</t>
+          <t>60823</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>65672</t>
+          <t>65321</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>102800</t>
+          <t>102617</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>485960</t>
+          <t>486521</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>517658</t>
+          <t>517838</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>646139</t>
+          <t>647143</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>680514</t>
+          <t>679290</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1144308</t>
+          <t>1141973</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1190795</t>
+          <t>1188525</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar un telefono en 2016</t>
+          <t>Población según si es capaz de usar un telefono en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,62 +7733,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4368</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62608</t>
+          <t>61952</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>97161</t>
+          <t>95701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>104680</t>
+          <t>104660</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -8041,97 +8041,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2217</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>12,61%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8008</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48776</t>
+          <t>48180</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62924</t>
+          <t>62959</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8497,97 +8497,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1924</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113771</t>
+          <t>113953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36395</t>
+          <t>36598</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45007</t>
+          <t>45022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153991</t>
+          <t>153981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164320</t>
+          <t>164488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13147</t>
+          <t>12940</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14251</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>192151</t>
+          <t>191926</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>201325</t>
+          <t>201413</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>85899</t>
+          <t>86106</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96657</t>
+          <t>96846</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>283194</t>
+          <t>282540</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>296795</t>
+          <t>296556</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11767</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13598</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>31782</t>
+          <t>31835</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>125118</t>
+          <t>125171</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137304</t>
+          <t>137703</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>135199</t>
+          <t>136233</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>151741</t>
+          <t>151746</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>266916</t>
+          <t>265933</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>286927</t>
+          <t>285801</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23155</t>
+          <t>21987</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23155</t>
+          <t>21987</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27673</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27673</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>371223</t>
+          <t>370770</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>393561</t>
+          <t>393888</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>371223</t>
+          <t>370770</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>393561</t>
+          <t>393888</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17165</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39257</t>
+          <t>38429</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20621</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28122</t>
+          <t>28529</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55340</t>
+          <t>54471</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>39286</t>
+          <t>39691</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69399</t>
+          <t>69845</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>557744</t>
+          <t>558402</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>576118</t>
+          <t>575653</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>699152</t>
+          <t>699800</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>731430</t>
+          <t>731170</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1264150</t>
+          <t>1264211</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1299510</t>
+          <t>1300815</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar un telefono en 2023</t>
+          <t>Población según si es capaz de usar un telefono en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,62 +11046,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3171</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3155</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -11124,97 +11124,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2973</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>601</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3442</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3655</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>104379</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -11252,7 +11252,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62158</t>
+          <t>62348</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168587</t>
+          <t>168625</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>456</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89794</t>
+          <t>89464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94534</t>
+          <t>94531</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42410</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46543</t>
+          <t>46535</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134826</t>
+          <t>134369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140582</t>
+          <t>140507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95387</t>
+          <t>95269</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101117</t>
+          <t>101101</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48547</t>
+          <t>48272</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52381</t>
+          <t>52378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145505</t>
+          <t>145972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152957</t>
+          <t>152848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12532,7 +12532,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>18328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>221040</t>
+          <t>220893</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>231330</t>
+          <t>231318</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>316852</t>
+          <t>317213</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>326400</t>
+          <t>326473</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>538780</t>
+          <t>539360</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>560767</t>
+          <t>559813</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14659</t>
+          <t>14470</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16683</t>
+          <t>17149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>470</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15021</t>
+          <t>14562</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85428</t>
+          <t>85203</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90591</t>
+          <t>90665</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>178967</t>
+          <t>179192</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>190282</t>
+          <t>190400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>267287</t>
+          <t>266284</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>280142</t>
+          <t>279187</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,47 +13341,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>10372</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>6422</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>16816</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>10372</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>6186</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>16693</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>19522</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33744</t>
+          <t>34188</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33542</t>
+          <t>33655</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>275605</t>
+          <t>275079</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>293591</t>
+          <t>291978</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278593</t>
+          <t>278251</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>295532</t>
+          <t>295661</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33886</t>
+          <t>33328</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18964</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40237</t>
+          <t>39890</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21283</t>
+          <t>21420</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>22415</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>53713</t>
+          <t>52577</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>34485</t>
+          <t>35702</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>67275</t>
+          <t>66480</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>610590</t>
+          <t>609732</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>624285</t>
+          <t>623426</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>933787</t>
+          <t>935315</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>982470</t>
+          <t>984612</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1554666</t>
+          <t>1554379</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1601391</t>
+          <t>1602324</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5405-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5405-Clase-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>918</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51903</t>
+          <t>52961</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58951</t>
+          <t>58999</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23299</t>
+          <t>23402</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78760</t>
+          <t>79554</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87749</t>
+          <t>87799</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41109</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>57188</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>5885</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8539</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62508</t>
+          <t>61833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70046</t>
+          <t>70052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18282</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84341</t>
+          <t>84702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93483</t>
+          <t>94227</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>16972</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22356</t>
+          <t>20723</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>238654</t>
+          <t>238166</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>252045</t>
+          <t>251905</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>74849</t>
+          <t>73850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83869</t>
+          <t>83770</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>316075</t>
+          <t>317683</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>333088</t>
+          <t>334278</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>10832</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11195</t>
+          <t>10047</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9074</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>969</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47661</t>
+          <t>48078</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83249</t>
+          <t>83358</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93949</t>
+          <t>93928</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135510</t>
+          <t>135785</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>148016</t>
+          <t>148212</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19765</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19892</t>
+          <t>19807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19992</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19059</t>
+          <t>19580</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>391633</t>
+          <t>392032</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>411071</t>
+          <t>411133</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>396420</t>
+          <t>394906</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>415365</t>
+          <t>413857</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>14125</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>39005</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28575</t>
+          <t>27269</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>26613</t>
+          <t>26635</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49867</t>
+          <t>50634</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>463495</t>
+          <t>463826</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>483789</t>
+          <t>483498</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>626134</t>
+          <t>627579</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>650983</t>
+          <t>650948</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1098117</t>
+          <t>1099846</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1128875</t>
+          <t>1130228</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37575</t>
+          <t>38563</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62143</t>
+          <t>61713</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>13085</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13691</t>
+          <t>15985</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47240</t>
+          <t>46292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59203</t>
+          <t>59400</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63106</t>
+          <t>62762</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76349</t>
+          <t>76327</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104389</t>
+          <t>104548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117539</t>
+          <t>117502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49219</t>
+          <t>49251</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>158063</t>
+          <t>157054</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>171178</t>
+          <t>171149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>18323</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19969</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31278</t>
+          <t>30645</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12905</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33141</t>
+          <t>32795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>190391</t>
+          <t>190383</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>212540</t>
+          <t>211716</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51639</t>
+          <t>52093</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59014</t>
+          <t>60095</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>246330</t>
+          <t>245822</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>268826</t>
+          <t>269968</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13444</t>
+          <t>12182</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>19718</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>10586</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27505</t>
+          <t>27306</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14817</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29769</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>19131</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39986</t>
+          <t>39941</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80689</t>
+          <t>80443</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94480</t>
+          <t>94466</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>146476</t>
+          <t>143627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>166574</t>
+          <t>165934</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>231742</t>
+          <t>232651</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>256634</t>
+          <t>258054</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26066</t>
+          <t>25482</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25713</t>
+          <t>25721</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33167</t>
+          <t>33113</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14270</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32105</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>342811</t>
+          <t>343805</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>367890</t>
+          <t>366989</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>346134</t>
+          <t>344844</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>370055</t>
+          <t>368905</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11646</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29849</t>
+          <t>28999</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>21079</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43958</t>
+          <t>45194</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36914</t>
+          <t>37076</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>65792</t>
+          <t>67293</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24726</t>
+          <t>25287</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>51864</t>
+          <t>52936</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>33906</t>
+          <t>34199</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>60823</t>
+          <t>61458</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>64534</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>102617</t>
+          <t>104351</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>486521</t>
+          <t>486612</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>517838</t>
+          <t>517510</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>647143</t>
+          <t>647466</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>679290</t>
+          <t>679982</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1141973</t>
+          <t>1144226</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1188525</t>
+          <t>1191897</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61952</t>
+          <t>62527</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29458</t>
+          <t>30412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>95701</t>
+          <t>95642</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>104660</t>
+          <t>104652</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48180</t>
+          <t>48793</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62959</t>
+          <t>63125</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>9776</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12489</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113953</t>
+          <t>113024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36598</t>
+          <t>36433</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45022</t>
+          <t>44996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153981</t>
+          <t>153692</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164488</t>
+          <t>164364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11023</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>13008</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15132</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>191926</t>
+          <t>192514</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>201413</t>
+          <t>201424</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86106</t>
+          <t>86038</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96846</t>
+          <t>96873</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282540</t>
+          <t>283366</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>296556</t>
+          <t>296809</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>9566</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14301</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21378</t>
+          <t>21501</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13737</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>32259</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>125171</t>
+          <t>124468</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137703</t>
+          <t>137866</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>136233</t>
+          <t>137293</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>151746</t>
+          <t>152461</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>265933</t>
+          <t>266581</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>285801</t>
+          <t>287198</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>23042</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>23042</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26096</t>
+          <t>26945</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26096</t>
+          <t>26945</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>370770</t>
+          <t>370757</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>393888</t>
+          <t>393804</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>370770</t>
+          <t>370757</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>393888</t>
+          <t>393804</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>26072</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16646</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38429</t>
+          <t>38870</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>21889</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28529</t>
+          <t>27332</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54471</t>
+          <t>54239</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>39691</t>
+          <t>41043</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69845</t>
+          <t>71607</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>558402</t>
+          <t>557263</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>575653</t>
+          <t>575894</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>699800</t>
+          <t>699636</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>731170</t>
+          <t>732257</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1264211</t>
+          <t>1263734</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1300815</t>
+          <t>1300235</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>612</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>612</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -11086,12 +11086,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>653</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>653</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -11232,27 +11232,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106952</t>
+          <t>119789</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104379</t>
+          <t>117208</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -11267,27 +11267,27 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64720</t>
+          <t>73906</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62348</t>
+          <t>70713</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -11302,27 +11302,27 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>171672</t>
+          <t>193695</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168625</t>
+          <t>191013</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>922</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>979</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>657</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1742</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>477</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>93031</t>
+          <t>102708</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89464</t>
+          <t>98698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94531</t>
+          <t>104233</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45398</t>
+          <t>53749</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42806</t>
+          <t>51002</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46535</t>
+          <t>54992</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>138429</t>
+          <t>156457</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134369</t>
+          <t>152181</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140507</t>
+          <t>158645</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>477</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -11928,12 +11928,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>795</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -11963,12 +11963,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -12076,12 +12076,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>99226</t>
+          <t>109663</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95269</t>
+          <t>106025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101101</t>
+          <t>111570</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51190</t>
+          <t>56112</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48272</t>
+          <t>52201</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52378</t>
+          <t>57539</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>150417</t>
+          <t>165775</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145972</t>
+          <t>161150</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152848</t>
+          <t>168326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>15967</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -12532,12 +12532,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18328</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>226832</t>
+          <t>248210</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>220893</t>
+          <t>241428</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>231318</t>
+          <t>252901</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>323600</t>
+          <t>127698</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>317213</t>
+          <t>124195</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>326473</t>
+          <t>129629</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>550432</t>
+          <t>375908</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>539360</t>
+          <t>369751</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>559813</t>
+          <t>381168</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>337</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>15945</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17149</t>
+          <t>18047</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>474</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>10522</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14562</t>
+          <t>15681</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>17939</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>88638</t>
+          <t>97441</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85203</t>
+          <t>94096</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90665</t>
+          <t>99394</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>185280</t>
+          <t>199317</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>179192</t>
+          <t>192593</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>190400</t>
+          <t>205174</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>273918</t>
+          <t>296758</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>266284</t>
+          <t>289132</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>279187</t>
+          <t>302882</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16184</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16816</t>
+          <t>17932</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>25699</t>
+          <t>27678</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19522</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34188</t>
+          <t>36436</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>25699</t>
+          <t>27678</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33655</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -13547,22 +13547,22 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>284897</t>
+          <t>305921</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>275079</t>
+          <t>295569</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>291978</t>
+          <t>314828</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>288101</t>
+          <t>309197</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278251</t>
+          <t>299088</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>295661</t>
+          <t>318088</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>320969</t>
+          <t>344879</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>320969</t>
+          <t>344879</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>320969</t>
+          <t>344879</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>324173</t>
+          <t>348155</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324173</t>
+          <t>348155</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>324173</t>
+          <t>348155</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>25510</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>19130</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33328</t>
+          <t>35345</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>31571</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18964</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39890</t>
+          <t>40462</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21420</t>
+          <t>21913</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>38933</t>
+          <t>41705</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22415</t>
+          <t>32310</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>52577</t>
+          <t>51696</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>52980</t>
+          <t>56218</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>35702</t>
+          <t>46061</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>66480</t>
+          <t>69639</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>617884</t>
+          <t>681088</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>609732</t>
+          <t>673101</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>623426</t>
+          <t>687086</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>955085</t>
+          <t>816703</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>935315</t>
+          <t>804039</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>984612</t>
+          <t>828522</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1572968</t>
+          <t>1497791</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1554379</t>
+          <t>1483257</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1602324</t>
+          <t>1511877</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1017836</t>
+          <t>883917</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1017836</t>
+          <t>883917</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1017836</t>
+          <t>883917</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1655888</t>
+          <t>1585580</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1655888</t>
+          <t>1585580</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1655888</t>
+          <t>1585580</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
